--- a/tests/Fixtures/Workbooks/policy-workbook.xlsx
+++ b/tests/Fixtures/Workbooks/policy-workbook.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Policies" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Policy votes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Divisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Display notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Divisions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,17 +587,10 @@
           <t>UNVERIFIED: nothing</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2">
         <f>COUNTIF('Policy votes'!$A$2:$A$400,$A2)</f>
         <v/>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>A test description.</t>
@@ -654,7 +648,6 @@
           <t>Also for testing</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Reviewer note</t>
@@ -664,12 +657,6 @@
         <f>COUNTIF('Policy votes'!$A$2:$A$400,$A3)</f>
         <v/>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>Another description.</t>
@@ -685,7 +672,6 @@
           <t>Against.</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,25 +694,10 @@
           <t>Dropped test policy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4">
         <f>COUNTIF('Policy votes'!$A$2:$A$400,$A4)</f>
         <v/>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,28 +705,10 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5">
         <f>COUNTIF('Policy votes'!$A$2:$A$400,$A5)</f>
         <v/>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -918,23 +871,6 @@
         <f>IF($B2="","",IFERROR(INDEX(Divisions!$B$2:$B$10,MATCH($B2,Divisions!$A$2:$A$10,0)),""))</f>
         <v/>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -966,23 +902,6 @@
         <f>IF($B3="","",IFERROR(INDEX(Divisions!$B$2:$B$10,MATCH($B3,Divisions!$A$2:$A$10,0)),""))</f>
         <v/>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1014,51 +933,12 @@
         <f>IF($B4="","",IFERROR(INDEX(Divisions!$B$2:$B$10,MATCH($B4,Divisions!$A$2:$A$10,0)),""))</f>
         <v/>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5">
         <f>IF($B5="","",IFERROR(INDEX(Divisions!$B$2:$B$10,MATCH($B5,Divisions!$A$2:$A$10,0)),""))</f>
         <v/>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1071,6 +951,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Policy ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Party or MP</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Note (public)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test Party</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Voted for the motion but opposed its main clause.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
